--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.07049619045643</v>
+        <v>3.58645563094917</v>
       </c>
       <c r="D2" t="n">
-        <v>31.88631830790977</v>
+        <v>5.181526725035337</v>
       </c>
       <c r="E2" t="n">
-        <v>6.459958822340167</v>
+        <v>1.049743308630277</v>
       </c>
       <c r="F2" t="n">
-        <v>11.38534234705404</v>
+        <v>1.850118131396282</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.150578545776094</v>
+        <v>1.486969013688615</v>
       </c>
       <c r="D3" t="n">
-        <v>9.115633613801689</v>
+        <v>1.481290462242774</v>
       </c>
       <c r="E3" t="n">
-        <v>6.459958822340167</v>
+        <v>1.049743308630277</v>
       </c>
       <c r="F3" t="n">
-        <v>11.38534234705404</v>
+        <v>1.850118131396282</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
